--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_capacities_tests.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_capacities_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81.20***</t>
+          <t>83.22***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.70***</t>
+          <t>14.16***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6669.47***</t>
+          <t>7125.58***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.72***</t>
+          <t>79.72***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.79***</t>
+          <t>115.59***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.20***</t>
+          <t>83.22***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.02***</t>
+          <t>4.67***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6609.96***</t>
+          <t>6946.77***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.37***</t>
+          <t>19.89***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.79***</t>
+          <t>115.59***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>81.20***</t>
+          <t>83.22***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.38***</t>
+          <t>4.65***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6612.96***</t>
+          <t>6946.56***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.40***</t>
+          <t>14.22***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.79***</t>
+          <t>115.59***</t>
         </is>
       </c>
     </row>
